--- a/tools/importer/reports/import-nav.report.xlsx
+++ b/tools/importer/reports/import-nav.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="166">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,60 @@
     <t>url</t>
   </si>
   <si>
+    <t>about-us.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>about-us</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>empty-section-hub</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:22:16.376Z</t>
+  </si>
+  <si>
+    <t>About us</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/about-us/</t>
+  </si>
+  <si>
+    <t>footer.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>footer</t>
+  </si>
+  <si>
+    <t>2026-10-05T18:08:40.243Z</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/</t>
+  </si>
+  <si>
+    <t>html-sitemap.report.json</t>
+  </si>
+  <si>
+    <t>html-sitemap</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:22:08.650Z</t>
+  </si>
+  <si>
+    <t>HTML Sitemap</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/html-sitemap/</t>
+  </si>
+  <si>
     <t>index.report.json</t>
   </si>
   <si>
@@ -46,19 +100,31 @@
     <t>index</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>content-landing-page</t>
   </si>
   <si>
-    <t>2026-10-05T16:04:59.519Z</t>
+    <t>2026-10-13T15:19:52.095Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
   </si>
   <si>
-    <t>https://www.destinationpet.com/</t>
+    <t>join-our-pack.report.json</t>
+  </si>
+  <si>
+    <t>join-our-pack</t>
+  </si>
+  <si>
+    <t>empty-top-level-hub</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:22:32.923Z</t>
+  </si>
+  <si>
+    <t>Join our pack</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/join-our-pack/</t>
   </si>
   <si>
     <t>live-webinar.report.json</t>
@@ -70,7 +136,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:40.821Z</t>
+    <t>2026-10-13T15:20:32.988Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -82,13 +148,10 @@
     <t>nav.report.json</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>nav</t>
   </si>
   <si>
-    <t>2026-10-05T17:23:53.482Z</t>
+    <t>2026-10-14T07:02:11.859Z</t>
   </si>
   <si>
     <t>our-locations.report.json</t>
@@ -100,7 +163,7 @@
     <t>our-locations</t>
   </si>
   <si>
-    <t>2026-10-05T16:06:12.248Z</t>
+    <t>2026-10-13T15:20:59.607Z</t>
   </si>
   <si>
     <t>Our Locations | Destination Pet</t>
@@ -109,6 +172,24 @@
     <t>https://www.destinationpet.com/our-locations/</t>
   </si>
   <si>
+    <t>privacy-policy.report.json</t>
+  </si>
+  <si>
+    <t>privacy-policy</t>
+  </si>
+  <si>
+    <t>legal-text-page</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:21:36.565Z</t>
+  </si>
+  <si>
+    <t>Privacy Policy | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/privacy-policy/</t>
+  </si>
+  <si>
     <t>sell-your-business.report.json</t>
   </si>
   <si>
@@ -118,7 +199,7 @@
     <t>sell-your-business</t>
   </si>
   <si>
-    <t>2026-10-05T16:06:18.273Z</t>
+    <t>2026-10-13T15:21:05.928Z</t>
   </si>
   <si>
     <t>Sell Your Veterinary | Destination Pet</t>
@@ -127,6 +208,21 @@
     <t>https://www.destinationpet.com/sell-your-business/</t>
   </si>
   <si>
+    <t>terms-and-conditions.report.json</t>
+  </si>
+  <si>
+    <t>terms-and-conditions</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:21:41.799Z</t>
+  </si>
+  <si>
+    <t>Terms and Conditions | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/terms-and-conditions/</t>
+  </si>
+  <si>
     <t>about-us/about.report.json</t>
   </si>
   <si>
@@ -136,7 +232,7 @@
     <t>about-us/about</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:05.121Z</t>
+    <t>2026-10-13T15:19:57.662Z</t>
   </si>
   <si>
     <t>About Us | Destination Pet, LLC</t>
@@ -145,6 +241,42 @@
     <t>https://www.destinationpet.com/about-us/about/</t>
   </si>
   <si>
+    <t>about-us/ccpa-request.report.json</t>
+  </si>
+  <si>
+    <t>about-us/ccpa-request</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:21:24.482Z</t>
+  </si>
+  <si>
+    <t>CCPA Request - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/about-us/ccpa-request/</t>
+  </si>
+  <si>
+    <t>about-us/destination-pet-foundation.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","columns-slider"]</t>
+  </si>
+  <si>
+    <t>about-us/destination-pet-foundation</t>
+  </si>
+  <si>
+    <t>hero-feature-showcase</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:21:50.145Z</t>
+  </si>
+  <si>
+    <t>Destination Pet Foundation - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/about-us/destination-pet-foundation/</t>
+  </si>
+  <si>
     <t>about-us/get-in-touch.report.json</t>
   </si>
   <si>
@@ -154,7 +286,7 @@
     <t>about-us/get-in-touch</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:11.137Z</t>
+    <t>2026-10-13T15:20:04.813Z</t>
   </si>
   <si>
     <t>Contact Us | Destination Pet, LLC</t>
@@ -163,13 +295,46 @@
     <t>https://www.destinationpet.com/about-us/get-in-touch/</t>
   </si>
   <si>
+    <t>about-us/meet-the-team.report.json</t>
+  </si>
+  <si>
+    <t>about-us/meet-the-team</t>
+  </si>
+  <si>
+    <t>empty-subsection-hub</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:22:25.293Z</t>
+  </si>
+  <si>
+    <t>Meet The Team</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/about-us/meet-the-team/</t>
+  </si>
+  <si>
+    <t>about-us/tradeshows-events.report.json</t>
+  </si>
+  <si>
+    <t>about-us/tradeshows-events</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:21:30.642Z</t>
+  </si>
+  <si>
+    <t>Tradeshows - Events - Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/about-us/tradeshows-events/</t>
+  </si>
+  <si>
     <t>join-our-pack/find-a-veterinary-externship.report.json</t>
   </si>
   <si>
     <t>join-our-pack/find-a-veterinary-externship</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:29.814Z</t>
+    <t>2026-10-13T15:20:23.797Z</t>
   </si>
   <si>
     <t>Find a Veterinary Externship - Destination Pet</t>
@@ -187,7 +352,7 @@
     <t>join-our-pack/life-at-dp</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:34.654Z</t>
+    <t>2026-10-13T15:20:27.908Z</t>
   </si>
   <si>
     <t>life at Destination Pet | Destination Pet</t>
@@ -205,7 +370,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:44.482Z</t>
+    <t>2026-10-13T15:20:36.986Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>
@@ -220,7 +385,7 @@
     <t>live-webinar/webinar-registration</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:55.598Z</t>
+    <t>2026-10-13T15:20:42.646Z</t>
   </si>
   <si>
     <t>Webinar Registration - Destination Pet</t>
@@ -235,7 +400,7 @@
     <t>live-webinar/webinar-viewing-previous</t>
   </si>
   <si>
-    <t>2026-10-05T16:06:01.387Z</t>
+    <t>2026-10-13T15:20:48.822Z</t>
   </si>
   <si>
     <t>Webinar Viewing Previous - Destination Pet</t>
@@ -250,7 +415,7 @@
     <t>live-webinar/webinars-for-pet</t>
   </si>
   <si>
-    <t>2026-10-05T16:06:07.499Z</t>
+    <t>2026-10-13T15:20:53.204Z</t>
   </si>
   <si>
     <t>Webinars for Pet - Destination Pet</t>
@@ -259,6 +424,27 @@
     <t>https://www.destinationpet.com/live-webinar/webinars-for-pet/</t>
   </si>
   <si>
+    <t>our-locations/location.report.json</t>
+  </si>
+  <si>
+    <t>["location-finder"]</t>
+  </si>
+  <si>
+    <t>our-locations/location</t>
+  </si>
+  <si>
+    <t>location-finder</t>
+  </si>
+  <si>
+    <t>2026-10-13T15:21:59.643Z</t>
+  </si>
+  <si>
+    <t>Spot our Location | Destination Pet</t>
+  </si>
+  <si>
+    <t>https://www.destinationpet.com/our-locations/location/</t>
+  </si>
+  <si>
     <t>sell-your-business/sell-your-pet-resort.report.json</t>
   </si>
   <si>
@@ -268,7 +454,7 @@
     <t>sell-your-business/sell-your-pet-resort</t>
   </si>
   <si>
-    <t>2026-10-05T16:06:25.160Z</t>
+    <t>2026-10-13T15:21:11.714Z</t>
   </si>
   <si>
     <t>Sell Your Pet Resort - Destination Pet</t>
@@ -286,7 +472,7 @@
     <t>sell-your-business/sell-your-veterinary-practice</t>
   </si>
   <si>
-    <t>2026-10-05T16:06:30.222Z</t>
+    <t>2026-10-13T15:21:16.461Z</t>
   </si>
   <si>
     <t>Sell your veterinary practice | Destination Pet</t>
@@ -301,7 +487,7 @@
     <t>about-us/meet-the-team/business-development-leaders</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:16.856Z</t>
+    <t>2026-10-13T15:20:11.055Z</t>
   </si>
   <si>
     <t>Business Development Leaders | Destination Pet</t>
@@ -316,7 +502,7 @@
     <t>about-us/meet-the-team/leadership</t>
   </si>
   <si>
-    <t>2026-10-05T16:05:23.559Z</t>
+    <t>2026-10-13T15:20:16.502Z</t>
   </si>
   <si>
     <t>Leadership - Meet the team | Destination Pet</t>
@@ -711,11 +897,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="49" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
@@ -787,42 +973,42 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>19</v>
       </c>
       <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
       </c>
       <c r="G4" t="s">
         <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -839,16 +1025,16 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -856,16 +1042,16 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
         <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>35</v>
@@ -891,7 +1077,7 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
         <v>41</v>
@@ -908,198 +1094,198 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="G9" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>52</v>
-      </c>
-      <c r="G9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>56</v>
       </c>
-      <c r="C10" t="s">
+      <c r="G10" t="s">
         <v>57</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>58</v>
-      </c>
-      <c r="G10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
         <v>62</v>
       </c>
-      <c r="C11" t="s">
+      <c r="G11" t="s">
         <v>63</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>64</v>
-      </c>
-      <c r="G11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
         <v>67</v>
       </c>
-      <c r="B12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="G12" t="s">
         <v>68</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>69</v>
-      </c>
-      <c r="G12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
         <v>72</v>
       </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
         <v>73</v>
       </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>74</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>75</v>
-      </c>
-      <c r="H13" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>77</v>
       </c>
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="s">
         <v>78</v>
       </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>79</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>80</v>
-      </c>
-      <c r="H14" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
         <v>82</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>83</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
         <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
       </c>
       <c r="F15" t="s">
         <v>85</v>
@@ -1125,7 +1311,7 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
         <v>91</v>
@@ -1142,7 +1328,7 @@
         <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
         <v>95</v>
@@ -1151,42 +1337,328 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H18" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" t="s">
+        <v>134</v>
+      </c>
+      <c r="G24" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" t="s">
+        <v>142</v>
+      </c>
+      <c r="H25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" t="s">
+        <v>148</v>
+      </c>
+      <c r="H26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H27" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" t="s">
+        <v>164</v>
+      </c>
+      <c r="H29" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
